--- a/data/trans_orig/IP31A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>37561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>39922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72728</t>
+          <t>72872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>35304</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53849</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>46696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94000</t>
+          <t>93392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122747</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148110</t>
+          <t>148207</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183021</t>
+          <t>185427</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164592</t>
+          <t>163641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194670</t>
+          <t>194487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185722</t>
+          <t>184540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219242</t>
+          <t>217877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360427</t>
+          <t>360612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>407657</t>
+          <t>403118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88538</t>
+          <t>88215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115520</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73984</t>
+          <t>73226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101231</t>
+          <t>100634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169663</t>
+          <t>169117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208483</t>
+          <t>205956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51451</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77881</t>
+          <t>78068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97354</t>
+          <t>97293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>65158</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84451</t>
+          <t>83630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148538</t>
+          <t>147999</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175230</t>
+          <t>175377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57292</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81045</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77144</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129855</t>
+          <t>130180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>163683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214635</t>
+          <t>214438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258790</t>
+          <t>260419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>277982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317411</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290222</t>
+          <t>289835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331255</t>
+          <t>330032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>579005</t>
+          <t>579315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>634396</t>
+          <t>634319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>145592</t>
+          <t>145990</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>179385</t>
+          <t>180674</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>121663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>155103</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>277797</t>
+          <t>273355</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>326757</t>
+          <t>323571</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32648</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42880</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>48206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66582</t>
+          <t>66507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87981</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32857</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>51451</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52657</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77238</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78516</t>
+          <t>77972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107388</t>
+          <t>107390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138449</t>
+          <t>138075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174723</t>
+          <t>176019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>167639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199204</t>
+          <t>198845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198330</t>
+          <t>200907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>232741</t>
+          <t>234049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376004</t>
+          <t>377014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>422280</t>
+          <t>422598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87685</t>
+          <t>87979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115578</t>
+          <t>115420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>73587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100399</t>
+          <t>101262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167977</t>
+          <t>167609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>206335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>23517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35526</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55672</t>
+          <t>56356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66378</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86276</t>
+          <t>86221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67719</t>
+          <t>68389</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88210</t>
+          <t>87327</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140162</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>169385</t>
+          <t>169412</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>66088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>90533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115804</t>
+          <t>115123</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150563</t>
+          <t>149930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198521</t>
+          <t>198925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242465</t>
+          <t>245693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274558</t>
+          <t>274571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315817</t>
+          <t>314002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315769</t>
+          <t>317316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358430</t>
+          <t>357538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599907</t>
+          <t>603062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659337</t>
+          <t>660538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>147506</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>125237</t>
+          <t>125972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159519</t>
+          <t>159914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>283448</t>
+          <t>282660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>331731</t>
+          <t>333096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>34643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>50814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77132</t>
+          <t>76413</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50892</t>
+          <t>51515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69114</t>
+          <t>68608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21732</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43789</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36476</t>
+          <t>36531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69967</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89151</t>
+          <t>88024</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>118468</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196512</t>
+          <t>196878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>227819</t>
+          <t>228653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207243</t>
+          <t>205732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239440</t>
+          <t>240686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>411870</t>
+          <t>412634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457292</t>
+          <t>458756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90703</t>
+          <t>90638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119121</t>
+          <t>118938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91958</t>
+          <t>91054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121761</t>
+          <t>120484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189407</t>
+          <t>190085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230714</t>
+          <t>230812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40516</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19991</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72278</t>
+          <t>72976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32333</t>
+          <t>32001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>45704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64654</t>
+          <t>64648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>84512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65905</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85359</t>
+          <t>84216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>134582</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162520</t>
+          <t>162250</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31370</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>46541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49621</t>
+          <t>50448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67147</t>
+          <t>67804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91037</t>
+          <t>91386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98856</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163794</t>
+          <t>164429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290351</t>
+          <t>290461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331169</t>
+          <t>328551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312317</t>
+          <t>312503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353543</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615312</t>
+          <t>615551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>670914</t>
+          <t>672474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>147562</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>184975</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>298482</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>348133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>111073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">

--- a/data/trans_orig/IP31A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14172</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9627</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19953</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15406</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10708</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22227</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10187</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21491</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14172</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8985</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19735</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33391</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26374</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40323</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30070</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23881</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36971</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23924</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37380</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33391</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26741</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39922</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54026</t>
+          <t>55066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72872</t>
+          <t>73510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19608</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13481</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24212</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17962</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30425</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17806</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>30689</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>33,03%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19608</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14111</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26027</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>27,87%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35304</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6793</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3608</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7099</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3197</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7062</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1174,57 +1174,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70368</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70368</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73296</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>73296</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>73296</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70368</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70368</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>70368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107863</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>93707</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123070</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>57133</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46696</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68359</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>46261</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>68127</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>16,33%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>107863</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121731</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148207</t>
+          <t>148991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185427</t>
+          <t>184912</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>201811</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>184770</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>216860</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>179237</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>163641</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>194487</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>163055</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>193839</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>201811</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>184540</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>217877</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360612</t>
+          <t>357571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403118</t>
+          <t>403021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87305</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74646</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102491</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>100843</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>88215</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115334</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87675</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116902</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>28,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87305</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73226</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>100634</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169117</t>
+          <t>170867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205956</t>
+          <t>210057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13426</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20212</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12652</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7831</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18650</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8053</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20664</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13426</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8423</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20076</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35438</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1743,57 +1743,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>410404</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>410404</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>410404</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>526</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>349865</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>349865</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>349865</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>410404</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>410404</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>410404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23485</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16912</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30868</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12269</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25626</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12134</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25154</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23485</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17264</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31430</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>52268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1973,72 +1973,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>75064</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>65874</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83357</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>56,25%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>49,36%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>62,46%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>87516</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>78068</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>97293</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>77381</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>96867</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>59,15%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>75064</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>65158</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>83630</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>56,25%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147999</t>
+          <t>148598</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175377</t>
+          <t>176155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30702</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23447</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>37569</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29082</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29318</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47515</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30702</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>38951</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>57453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8434</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4793</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9610</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8506</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2312,57 +2312,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>133458</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>133458</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>133458</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147957</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147957</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147957</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>133458</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>133458</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>133458</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2429,72 +2429,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>145519</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>127882</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>160872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23,69%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>90618</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>76393</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>105420</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>77389</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>105337</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>15,87%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>145519</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>130180</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>163683</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214438</t>
+          <t>215544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>260419</t>
+          <t>258451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2542,72 +2542,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>310266</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>291620</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>333678</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>50,51%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>47,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>296824</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>277982</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>316381</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>276946</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>314468</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>51,97%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>48,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>310266</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>289835</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>330032</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>50,51%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>579315</t>
+          <t>578970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>634319</t>
+          <t>633343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -2655,72 +2655,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>137615</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>120845</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>155351</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>162624</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>180674</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>145230</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>181106</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,47%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>137615</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>121663</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>155103</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>273355</t>
+          <t>275181</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>323571</t>
+          <t>325835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -2773,67 +2773,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>20830</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14720</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28633</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>21052</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>14378</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>29014</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15212</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>28930</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>20830</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>14290</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>28632</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2881,57 +2881,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>614230</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>614230</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>614230</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>851</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>571118</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>571118</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>571118</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>614230</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>614230</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>614230</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3061,7 +3061,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3229,72 +3229,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10167</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5765</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16012</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9795</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14758</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14805</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10167</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15803</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -3342,107 +3342,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40720</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33038</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47910</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36426</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29486</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43134</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29846</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43519</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>48,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>57,75%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>77146</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>67496</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>87041</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>50,73%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>57,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40720</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34376</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48206</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,09%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>62,86%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>77146</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>66507</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>86564</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>43,74%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -3455,72 +3455,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15665</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29232</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38,12%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19882</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26205</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>14144</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>26308</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>26,38%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22200</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16189</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28403</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51451</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -3568,72 +3568,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7997</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9260</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15020</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14516</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3605</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8203</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -3681,57 +3681,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76693</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76693</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76693</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75363</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>75363</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>75363</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>76693</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76693</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3798,72 +3798,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>79346</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>106801</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>63682</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52288</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>76261</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>52640</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>76579</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>17,17%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>77972</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>107390</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138075</t>
+          <t>137781</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176019</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -3911,72 +3911,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>217215</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>199578</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>233327</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>182624</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>167639</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>198845</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>168021</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>199442</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>217215</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>200907</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>234049</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377014</t>
+          <t>375994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>422598</t>
+          <t>424495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -4024,72 +4024,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86164</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72405</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99736</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>100880</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87979</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115420</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87651</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>115602</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>27,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86164</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73587</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101262</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167609</t>
+          <t>166756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>206335</t>
+          <t>207983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -4137,72 +4137,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16447</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10790</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23496</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16854</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31140</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16323</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>31986</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10664</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23517</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -4250,57 +4250,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>412087</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>412087</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>412087</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>370801</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>370801</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>370801</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>412087</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>412087</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>412087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4367,72 +4367,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30041</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22869</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38887</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>14816</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9893</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21818</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9791</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21741</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30041</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22531</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39447</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56356</t>
+          <t>56122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -4480,72 +4480,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>78591</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68528</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>88380</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>46,49%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>59,96%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76530</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>65902</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>86221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>66622</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>86670</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>54,18%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>78591</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>68389</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>87327</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>53,32%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142032</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>169412</t>
+          <t>168247</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -4593,72 +4593,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33648</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25040</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42281</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>44067</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35031</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>53389</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33648</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26235</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42960</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>66968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90533</t>
+          <t>91536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -4706,74 +4706,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>5850</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9426</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4819,57 +4819,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147396</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147396</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147396</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>141263</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>141263</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>141263</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>147396</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>147396</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>147396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4936,72 +4936,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>132469</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>116450</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>150635</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>88293</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>73427</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>102853</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>74518</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>102953</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>15,03%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>132469</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>115123</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>149930</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198925</t>
+          <t>199256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245693</t>
+          <t>242914</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -5049,72 +5049,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>336527</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>315730</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>357807</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,63%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>56,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>427</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>295580</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>274571</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>314002</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>276244</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>314757</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>50,32%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>53,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>336527</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>317316</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>357538</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>603062</t>
+          <t>603077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>660538</t>
+          <t>661743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -5162,72 +5162,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>142012</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>124655</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>159934</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,32%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>19,59%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>25,14%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>164829</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>147882</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>182488</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>148705</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>184691</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,06%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>142012</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>125972</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>159914</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>282660</t>
+          <t>282181</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>333096</t>
+          <t>331629</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -5275,72 +5275,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25169</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17316</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>33628</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>38724</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>29671</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>29545</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>48843</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>25169</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>17810</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>34643</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50814</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76413</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5388,57 +5388,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>636177</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>636177</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>636177</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>847</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>587427</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>587427</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>587427</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>636177</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>636177</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>636177</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5568,7 +5568,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5741,67 +5741,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2278</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7092</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2885</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6882</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2278</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -5849,72 +5849,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35844</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29405</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42001</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24164</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18510</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18442</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29185</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>35844</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29509</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41424</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>59,63%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>68445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -5962,72 +5962,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19292</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13344</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25710</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15785</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10216</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20816</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>32,33%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19292</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13829</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25839</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42820</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -6075,72 +6075,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2693</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5995</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2938</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10975</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10310</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2693</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6095</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6188,57 +6188,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60107</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>60107</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>48829</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>48829</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>48829</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>60107</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>60107</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>60107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6305,72 +6305,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>57635</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47081</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>69880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45696</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36531</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>55587</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36920</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>58138</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,6%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>57635</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>46026</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>69900</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88024</t>
+          <t>87919</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118468</t>
+          <t>118856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -6418,72 +6418,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>223160</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>205514</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>239366</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>211670</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>196878</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>228653</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>196821</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>227170</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>223160</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>205732</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>240686</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>54,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>412634</t>
+          <t>411865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>458756</t>
+          <t>456993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -6531,72 +6531,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104580</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>90992</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>120130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>105105</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90638</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>118938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>91671</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>119323</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>104580</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>91054</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>120484</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190085</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230812</t>
+          <t>230481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -6644,72 +6644,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27689</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19526</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36693</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31425</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23438</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41461</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23533</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>40222</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27689</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37251</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47990</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72976</t>
+          <t>73729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -6757,57 +6757,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>413064</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>413064</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>413064</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>593</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>393896</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>393896</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>393896</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>413064</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>413064</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>413064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6874,72 +6874,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24383</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17479</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32019</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>11576</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7032</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17684</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7617</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18128</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24383</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17718</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32001</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45704</t>
+          <t>45541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -6992,67 +6992,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>74823</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>65334</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>85075</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>49,41%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>56,19%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>74391</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>64648</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>84512</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>64013</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>83782</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>53,42%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>46,42%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>60,68%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>74823</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>63892</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>84216</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>49,41%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>134476</t>
+          <t>134650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162250</t>
+          <t>162839</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -7100,72 +7100,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40613</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32018</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49754</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>32,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38126</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29261</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46541</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29834</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46908</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40613</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32618</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50448</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>26,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>66465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91386</t>
+          <t>91796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -7213,72 +7213,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11601</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18420</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>15177</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10007</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23077</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9782</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11601</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6410</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>18051</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35249</t>
+          <t>35628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -7326,57 +7326,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>151419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>151419</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>151419</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>139269</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>139269</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>139269</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>151419</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>151419</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>151419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7443,72 +7443,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>84296</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>71589</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>99894</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>60156</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>49649</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>73240</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>48705</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>72324</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>84296</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>70514</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>99014</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128304</t>
+          <t>127572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164429</t>
+          <t>165099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -7556,72 +7556,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>333828</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>314751</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>353717</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>53,45%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>50,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>56,63%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>461</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>310225</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>290461</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>328551</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>291534</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>330009</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>53,3%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>49,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>333828</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>312503</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>353626</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>53,45%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615551</t>
+          <t>615362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672474</t>
+          <t>672074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -7669,72 +7669,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>164485</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>149219</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>185567</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,71%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>159016</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>142594</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>177703</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>141198</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>176387</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>27,32%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>164485</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>147562</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>183915</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,33%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>297469</t>
+          <t>299507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>348133</t>
+          <t>347439</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -7782,72 +7782,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>41982</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>31536</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>54570</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>52596</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>41960</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>64618</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>64196</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>9,04%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>41982</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>32933</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>54212</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>79562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111073</t>
+          <t>110822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -7895,57 +7895,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>624591</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>624591</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>624591</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>874</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>581994</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>581994</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>581994</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>624591</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>624591</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>624591</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
